--- a/data/trans_orig/IP25A01_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25A01_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18591</t>
+          <t>18193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>849</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22674</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17041</t>
+          <t>17022</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11086</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26736</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31056</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47975</t>
+          <t>48192</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47285</t>
+          <t>49025</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70792</t>
+          <t>72189</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>85523</t>
+          <t>84769</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112966</t>
+          <t>114732</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>39390</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>56750</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52811</t>
+          <t>51809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77599</t>
+          <t>76320</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96985</t>
+          <t>96581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125208</t>
+          <t>126576</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,16%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33130</t>
+          <t>33487</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34170</t>
+          <t>34073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49538</t>
+          <t>49964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35617</t>
+          <t>35574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52298</t>
+          <t>51658</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74397</t>
+          <t>73414</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97917</t>
+          <t>96153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33162</t>
+          <t>33299</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47837</t>
+          <t>49375</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28095</t>
+          <t>28024</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>43534</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64916</t>
+          <t>65009</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87847</t>
+          <t>88047</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>379</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>13211</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25018</t>
+          <t>25307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26651</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41332</t>
+          <t>41482</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43448</t>
+          <t>43429</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62607</t>
+          <t>62518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21055</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33970</t>
+          <t>33380</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15587</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30686</t>
+          <t>29479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40024</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59150</t>
+          <t>60217</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>19668</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>21849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27406</t>
+          <t>27783</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24312</t>
+          <t>25080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45792</t>
+          <t>45315</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66815</t>
+          <t>61221</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>120169</t>
+          <t>118443</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>79058</t>
+          <t>78942</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106712</t>
+          <t>108132</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>155300</t>
+          <t>150234</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>216782</t>
+          <t>217555</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,16%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74826</t>
+          <t>74578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139149</t>
+          <t>138934</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84101</t>
+          <t>83205</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>113399</t>
+          <t>113462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169420</t>
+          <t>168367</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>241375</t>
+          <t>246762</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,49 +3021,49 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>5100</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2079</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>11123</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
           <t>6,85%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>5100</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2217</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>11493</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>20139</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40620</t>
+          <t>39817</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>39165</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56963</t>
+          <t>57073</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62536</t>
+          <t>62261</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>93312</t>
+          <t>91728</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>109808</t>
+          <t>109735</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>144269</t>
+          <t>143953</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>37969</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>55933</t>
+          <t>56513</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>52299</t>
+          <t>53751</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>86007</t>
+          <t>85556</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>97499</t>
+          <t>97496</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>136860</t>
+          <t>136562</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23188</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>25293</t>
+          <t>25798</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40699</t>
+          <t>39799</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29302</t>
+          <t>29450</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>44470</t>
+          <t>44868</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>59688</t>
+          <t>60587</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>81231</t>
+          <t>80879</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,18%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17193</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30900</t>
+          <t>30499</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34229</t>
+          <t>34658</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>40270</t>
+          <t>40175</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>60376</t>
+          <t>60245</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>36521</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>27827</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>31283</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>56896</t>
+          <t>55721</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>47699</t>
+          <t>46970</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>77091</t>
+          <t>77724</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>56495</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>85943</t>
+          <t>86445</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>110489</t>
+          <t>112094</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>154681</t>
+          <t>150349</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>236379</t>
+          <t>239920</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>306194</t>
+          <t>307946</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>320894</t>
+          <t>317864</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>375320</t>
+          <t>376459</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>581454</t>
+          <t>581041</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>666423</t>
+          <t>663624</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>254170</t>
+          <t>256143</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>335888</t>
+          <t>334948</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>283904</t>
+          <t>283011</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>342981</t>
+          <t>346385</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>557725</t>
+          <t>558570</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>653565</t>
+          <t>651095</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A01_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25A01_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2461</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6356</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7161</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2857</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18193</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27657</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>57821</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49328</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67696</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>40,35%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>55,37%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>39024</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>30984</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>48192</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>38,41%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,5%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>47,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60452</t>
+          <t>40199</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49025</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72189</t>
+          <t>48839</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>99475</t>
+          <t>98020</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84769</t>
+          <t>84649</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114732</t>
+          <t>111010</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>52321</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42796</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>61106</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35,01%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>49,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>47768</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39390</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56750</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>47,02%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>38,77%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>55,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63298</t>
+          <t>47682</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51809</t>
+          <t>39724</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76320</t>
+          <t>56412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>111066</t>
+          <t>100002</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96581</t>
+          <t>87223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126576</t>
+          <t>113532</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>51,04%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>101599</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101599</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>101599</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>100172</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>100172</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>100172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>238117</t>
+          <t>222424</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>238117</t>
+          <t>222424</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>238117</t>
+          <t>222424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5379</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2820</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>6539</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>9810</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14185</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8537</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20354</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9023</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4896</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14419</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22117</t>
+          <t>15080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>23265</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17434</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>31671</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>42541</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34310</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50279</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>55,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>41675</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34073</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>49964</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>44,2%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,14%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52,99%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43712</t>
+          <t>43323</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35574</t>
+          <t>36089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51658</t>
+          <t>52869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>85387</t>
+          <t>85863</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73414</t>
+          <t>74438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96153</t>
+          <t>97226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33718</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26325</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>42219</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>36,89%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>46,19%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>40772</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>33299</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>49375</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>43,24%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>35,32%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>52,37%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35650</t>
+          <t>40851</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28024</t>
+          <t>32221</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43534</t>
+          <t>48715</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>76421</t>
+          <t>74570</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65009</t>
+          <t>63692</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88047</t>
+          <t>86876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,31%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>94290</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>94290</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>94290</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96206</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96206</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>189863</t>
+          <t>187604</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>189863</t>
+          <t>187604</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189863</t>
+          <t>187604</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,107 +1858,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5117</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5026</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2602</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6577</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3792</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2594</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6106</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2991</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11668</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10,86%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>20,49%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3949</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1366</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>7867</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17372</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>31027</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24338</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>37580</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>54,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42,74%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>66,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>18539</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13211</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25307</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>35,75%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>48,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34263</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26534</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41482</t>
+          <t>26195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>52802</t>
+          <t>50289</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43429</t>
+          <t>41370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62518</t>
+          <t>59542</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,92%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18868</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12781</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>25234</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,14%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>27588</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>21055</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33380</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>53,2%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>40,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>64,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22103</t>
+          <t>27985</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>21634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29479</t>
+          <t>35064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>49691</t>
+          <t>46853</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40308</t>
+          <t>37972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60217</t>
+          <t>56291</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10630</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19668</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14935</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21849</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>19255</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27783</t>
+          <t>22359</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>34190</t>
+          <t>32513</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25080</t>
+          <t>24166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45315</t>
+          <t>42361</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>86476</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>73602</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>101534</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>42,92%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>36,53%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>50,4%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>99680</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>61221</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>118443</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>46,15%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>28,34%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>54,83%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>92866</t>
+          <t>87296</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>78942</t>
+          <t>76923</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108132</t>
+          <t>98132</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>192546</t>
+          <t>173772</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>150234</t>
+          <t>154350</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>217555</t>
+          <t>189915</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>90510</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>76361</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>106310</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>44,92%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>37,9%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>52,77%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>96498</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>74578</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>138934</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>44,67%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>34,52%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>64,32%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>98311</t>
+          <t>70017</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83205</t>
+          <t>59147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>113462</t>
+          <t>81154</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>194809</t>
+          <t>160527</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>168367</t>
+          <t>144362</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>246762</t>
+          <t>181022</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>201470</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>201470</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>201470</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>216014</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>216014</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>216014</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>217694</t>
+          <t>176673</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>217694</t>
+          <t>176673</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>217694</t>
+          <t>176673</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>378143</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>378143</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>378143</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,67 +3001,67 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>4264</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>8520</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>5100</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2079</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>11123</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10641</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5728</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>16737</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>17521</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>11065</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>28560</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>24,43%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>28971</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20139</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39817</t>
+          <t>35438</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>72231</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>58060</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>84808</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>48,82%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>39,25%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>57,33%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>48206</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>39165</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>57073</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>33,5%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>48,81%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>79317</t>
+          <t>50061</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62261</t>
+          <t>41856</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91728</t>
+          <t>59180</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>127523</t>
+          <t>122292</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>109735</t>
+          <t>105567</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>143953</t>
+          <t>137817</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>60382</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>47807</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>76380</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>40,81%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>32,31%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>51,63%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>46961</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>37969</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>56513</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>40,16%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>32,47%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>66392</t>
+          <t>46957</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>53751</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>85556</t>
+          <t>55765</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>113353</t>
+          <t>107338</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>97496</t>
+          <t>91195</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>136562</t>
+          <t>124595</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>147940</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>147940</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>147940</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>116923</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>116923</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>116923</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>162259</t>
+          <t>116197</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>162259</t>
+          <t>116197</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162259</t>
+          <t>116197</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>279182</t>
+          <t>264136</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>279182</t>
+          <t>264136</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>279182</t>
+          <t>264136</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,72 +3565,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3655</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>3357</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>7276</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>13067</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>14650</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -3791,72 +3791,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>35621</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>28596</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>43406</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>52,41%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>42,08%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>63,86%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>32869</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>25798</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>39799</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>48,76%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>38,27%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>59,04%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>37440</t>
+          <t>35032</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29450</t>
+          <t>28228</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>44868</t>
+          <t>42885</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,22 +3866,22 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>70309</t>
+          <t>70653</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>60587</t>
+          <t>59767</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>80879</t>
+          <t>81573</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -3904,72 +3904,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>24429</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>17912</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>31889</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>35,94%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>26,36%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>46,92%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>23888</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>17382</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>30499</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>35,43%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>25,78%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>45,24%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>26263</t>
+          <t>24648</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18711</t>
+          <t>18090</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34658</t>
+          <t>31481</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>50151</t>
+          <t>49077</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>40175</t>
+          <t>40121</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>60245</t>
+          <t>60276</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -4017,57 +4017,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>67965</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>67965</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>67965</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>67413</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>67413</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>67413</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>71613</t>
+          <t>69166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>71613</t>
+          <t>69166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>71613</t>
+          <t>69166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>139026</t>
+          <t>137130</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>139026</t>
+          <t>137130</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>139026</t>
+          <t>137130</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4134,72 +4134,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>16697</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>10128</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>25487</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>24259</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>16469</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>36521</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11501</t>
+          <t>14913</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>29961</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>41773</t>
+          <t>38054</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31283</t>
+          <t>28425</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55721</t>
+          <t>49860</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -4247,57 +4247,57 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>65324</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>52194</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>79299</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>11,53%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>60375</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>46970</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>77724</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>69929</t>
+          <t>57226</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>56495</t>
+          <t>45958</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>86445</t>
+          <t>70182</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>130304</t>
+          <t>122550</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>112094</t>
+          <t>104688</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>150349</t>
+          <t>144126</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -4360,72 +4360,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>325717</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>301254</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>353953</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>47,34%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>43,79%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>51,45%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>400</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>279993</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>239920</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>307946</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>43,2%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>47,52%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>348048</t>
+          <t>275172</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>317864</t>
+          <t>256199</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>376459</t>
+          <t>297181</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>628041</t>
+          <t>600889</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>581041</t>
+          <t>566325</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>663624</t>
+          <t>632722</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -4473,72 +4473,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>280228</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>254433</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>307909</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>40,73%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>36,98%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>44,76%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>399</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>283474</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>256143</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>334948</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>43,74%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>39,52%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>51,68%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>312017</t>
+          <t>258139</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>283011</t>
+          <t>238879</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>346385</t>
+          <t>276984</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>595492</t>
+          <t>538367</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>558570</t>
+          <t>505735</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>651095</t>
+          <t>574323</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -4586,57 +4586,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>687965</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>687965</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>687965</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>916</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>648101</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>648101</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>648101</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>747508</t>
+          <t>611895</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>747508</t>
+          <t>611895</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>747508</t>
+          <t>611895</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1395610</t>
+          <t>1299860</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1395610</t>
+          <t>1299860</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1395610</t>
+          <t>1299860</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
